--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode5.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode5.xlsx
@@ -9,10 +9,9 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="G1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="G2a" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="G2b" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="G3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="G4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="G2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="G3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="G4" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:D13"/>
+  <dimension ref="C2:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="2" max="2"/>
@@ -485,14 +484,14 @@
     <row r="5">
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Total test cases: 12</t>
+          <t>Total test cases: 13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>High / Medium / Low: 9 / 3 / 0</t>
+          <t>High / Medium / Low: 10 / 3 / 0</t>
         </is>
       </c>
     </row>
@@ -511,7 +510,7 @@
     <row r="9">
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G1 — ขาย (Sale — Mode 5, FG Production)</t>
+          <t>G1 — ขาย (Sale — สินค้าสำเร็จรูปที่ต้องผลิตจาก Slab)</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -521,41 +520,31 @@
     <row r="10">
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>G2a — ผลิต — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ)</t>
+          <t>G2 — ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G2b — ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง)</t>
+          <t>G3 — จัดส่ง + ขายซ้ำ — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ)</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>G3 — จัดส่ง (Delivery)</t>
+          <t>G4 — บัญชี (Accounting + Payment)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>G4 — บัญชี (Accounting)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -589,7 +578,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G1. ขาย (Sale — Mode 5, FG Production) — ADR-029 — เพิ่มบรรทัดสินค้าสำเร็จรูป (FG) แล้วยืนยันคำสั่งขาย</t>
+          <t>G1. ขาย (Sale — สินค้าสำเร็จรูปที่ต้องผลิตจาก Slab) — ADR-029 — ขายสินค้า FG (เช่น Countertop) ที่ยังไม่ได้ผลิตจริงได้เลย</t>
         </is>
       </c>
     </row>
@@ -663,37 +652,35 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>เพิ่มบรรทัดสินค้าสำเร็จรูป (FG) ในใบสั่งขาย</t>
+          <t>เพิ่มบรรทัดสินค้า FG (Finished Good) ใน Sale Order ใหม่</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>มี Slab (วัตถุดิบตั้งต้นของ FG นี้) อยู่ในสต็อกที่ไหนสักแห่งแล้ว (ไม่จำเป็นต้องว่าง — ระบบจะเช็คให้เองตอน Confirm)</t>
+          <t>มี Slab พร้อมอยู่แล้วในสต็อกที่สถานีผลิต (Stone Production) จาก Material ที่ตั้งค่า FG ไว้ (มี Block/Slab/FG ครบ 3 สินค้า)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>1. เปิด Sales &gt; Orders &gt; New
 2. เลือกลูกค้า
-3. เพิ่มบรรทัด เลือกสินค้าสำเร็จรูป (FG)
-4. กรอกจำนวนที่ต้องการขาย</t>
+3. เพิ่มบรรทัด เลือกสินค้า FG ของ Material นั้น</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
-สินค้า = "Carrara White - Countertop"
-จำนวน = 3</t>
+สินค้า = E2E Mode5 Fresh Test - Countertop</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เพิ่มบรรทัดสำเร็จ ราคาต่อหน่วยขึ้นตามราคาตั้งต้นของสินค้า — ตัวอย่างจริง: 15,000.00 บาท/หน่วย × 3 = 45,000.00 + VAT 7% = 48,150.00 บาท</t>
+          <t>เพิ่มบรรทัดสำเร็จ ราคาต่อหน่วยขึ้นเป็นราคาตั้งต้นของสินค้า FG (ตัวอย่างจริง: 8,500/หน่วย)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H4" s="7" t="n"/>
@@ -710,7 +697,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ยืนยัน (Confirm) Sale Order</t>
+          <t>ยืนยัน (Confirm) Sale Order — ยังไม่มี FG ในสต็อกเลย</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -730,7 +717,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>SO เปลี่ยนสถานะเป็น Sales Order เกิด Delivery Order อัตโนมัติ 1 ใบ — ถ้า FG ที่ขายมีสต็อกว่างพอ บรรทัดจะไม่มีปุ่ม "Produce FG" เลย (ไปต่อที่ G2a) แต่ถ้าไม่พอ ปุ่ม "Cut to Order"/"Produce FG" จะปรากฏให้กดต่อ (ไปต่อที่ G2b) — ตัวอย่างจริง (กรณีสต็อกไม่พอ): S00112 ยอดรวม 48,150.00 บาท, ปุ่ม Produce FG ปรากฏที่บรรทัด</t>
+          <t>SO เปลี่ยนสถานะเป็น Sales Order ยอดรวม 9,095.00 บาท (รวม VAT) — บรรทัดสินค้า FG ปรากฏลิงก์ "Produce FG" ให้กดเพื่อผลิต เพราะยังไม่มีสต็อก FG เลย — ตัวอย่างจริง: S00127</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -758,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -778,7 +765,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G2a. ผลิต — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ) — ระบบเช็คสต็อกว่างของ FG เองก่อนเสมอ — เพิ่งแก้ไขให้ถูกต้อง 2026-09-07</t>
+          <t>G2. ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง) — ADR-029, stone.fg.production.wizard — เปิด wizard "Produce FG" ตัดจาก Slab ที่มีอยู่</t>
         </is>
       </c>
     </row>
@@ -852,28 +839,27 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>ระบบข้ามขั้นตอนผลิต เมื่อ FG มีสต็อกว่างพออยู่แล้ว</t>
+          <t>เปิด wizard "Produce FG" — ระบบจับคู่ Slab ที่จะใช้ให้อัตโนมัติ</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>สินค้า FG ตัวนี้มีสต็อกว่าง (ไม่ถูกจองไปกับออเดอร์อื่น) พอกับจำนวนที่จะขาย</t>
+          <t>ทำ TC-E2E-M5-02 เสร็จแล้ว มี Slab พร้อมอยู่ที่สถานีผลิตแล้ว (ย้ายด้วย Internal Transfer ล่วงหน้า)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เพิ่มบรรทัดสินค้า FG ในใบสั่งขายเหมือน TC-E2E-M5-01
-2. กด Confirm เหมือน TC-E2E-M5-02</t>
+          <t>1. กดลิงก์ "Produce FG" บนบรรทัดสินค้า FG ของ Sale Order</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>สินค้า = "Carrara White - Countertop" จำนวน = 2 (ตอนนั้นมีสต็อกว่างเหลือ 4 หน่วยจากการผลิตเผื่อไว้ใน G2b)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>บรรทัดไม่มีปุ่ม "Produce FG" ปรากฏเลย (ต่างจาก TC-E2E-M5-02) และไม่ขึ้นแถวในหน้า Factory Worklist เลย — ไปต่อที่การจัดส่งได้ทันทีโดยไม่ต้องผลิตอะไรเพิ่ม — ตัวอย่างจริง: S00113 ยอดรวม 32,100.00 บาท</t>
+          <t>เปิด wizard สำเร็จ ช่อง "Slab to Consume" เติมให้อัตโนมัติเป็น Slab ตัวแรกที่มี Material ตรงกันและสถานะ Available (v1: จับคู่ตาม Material อย่างเดียว) พร้อมบรรทัดผลผลิตเริ่มต้น 1 บรรทัดตรงกับสินค้าที่ขาย จำนวน 1 — ตัวอย่างจริง: Slab BLK-26-0029 #1</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -881,15 +867,100 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>✅ เพิ่งแก้ไข 2026-09-07: ก่อนหน้านี้ระบบไม่เคยเช็คสต็อกของ FG เอง จะขึ้นเตือนให้ผลิตซ้ำทุกครั้งแม้มี FG เหลือพอขายอยู่แล้ว — ตอนนี้เช็คให้อัตโนมัติแล้วจากสต็อก "ว่างจริง" ที่ไม่ถูกจองไปกับออเดอร์อื่น</t>
-        </is>
-      </c>
+      <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-04</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ปรับจำนวนผลผลิตแล้วกด "Produce" — สร้าง Manufacturing Order</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-03 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>1. แก้ไขจำนวนในบรรทัดผลผลิตจาก 1 เป็น 2
+2. กดปุ่ม "Produce"</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>จำนวนผลผลิต = 2</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>สร้าง Manufacturing Order สำเร็จ ยืนยันอัตโนมัติทันที (Confirmed) ระบบเติม Bill of Material ให้อัตโนมัติจาก FG Material ที่เลือก จำนวนที่จะผลิต = 2.00 Slab ที่เลือกถูกจับจองเป็นวัตถุดิบ (To Consume 1.00, Available) ผูกกับบรรทัด SO เดิม ("For Sale Order Line") — ตัวอย่างจริง: EG01/STFG/00015</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>ผลผลิตต่อ Slab กำหนดตอนผลิตจริง ไม่ใช่อัตราตายตัว (ADR-029) — เคสนี้ตั้งใจผลิต 2 หน่วยจาก Slab เดียว แม้บรรทัด SO ต้องการแค่ 1 หน่วย เพื่อเผื่อสต็อกไว้ขายลูกค้ารายถัดไป (ดู TC-E2E-M5-07)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-05</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>กด "Complete FG Production" — ได้สินค้า FG จริงเข้าสต็อก</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-04 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1. กดปุ่ม "Complete FG Production" บน Manufacturing Order</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Manufacturing Order เสร็จสมบูรณ์ (สถานะ Done) จำนวนที่ผลิตจริง = 2.00/2.00 ได้ Lot/Serial ใหม่ของสินค้า FG (ตัวอย่างจริง: FG-EG01/STFG/00015) Slab ที่ใช้เป็นวัตถุดิบเปลี่ยนสถานะเป็น Consumed หมดสภาพขายต่อ สินค้า FG 2 หน่วยเข้าสต็อกจริง</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -900,6 +971,243 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>G3. จัดส่ง + ขายซ้ำ — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ) — ส่งของบรรทัดแรก แล้วขายลูกค้าใหม่ด้วยสต็อกส่วนเกินที่เหลือ ไม่ต้องผ่าน wizard อีก</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-06</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>จัดส่งใบส่งของของบรรทัดแรก (SO1)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-05 เสร็จแล้ว มีสินค้า FG พร้อมส่งแล้ว</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบส่งของ (Delivery) ที่เกิดขึ้นอัตโนมัติของ S00127
+2. กดปุ่ม Validate</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>ใบส่งของเปลี่ยนสถานะเป็น Done สำเร็จทันที (จองสต็อกไว้ให้แล้วตั้งแต่ผลิตเสร็จ) — ตัวอย่างจริง: EG01/OUT/00081</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-07</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>สร้าง Sale Order ใหม่ขายสินค้า FG ตัวเดียวกันอีกครั้ง — ใช้สต็อกส่วนเกิน</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว มีสินค้า FG เหลือในสต็อก 1 หน่วยจากการผลิตครั้งก่อน</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Sales &gt; Orders &gt; New
+2. เลือกลูกค้าเดิม
+3. เพิ่มบรรทัด เลือกสินค้า FG ตัวเดียวกัน จำนวน 1
+4. กด Confirm</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
+สินค้า = E2E Mode5 Fresh Test - Countertop
+จำนวน = 1</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>SO ยืนยันสำเร็จ ยอดรวม 9,095.00 บาทเท่าเดิม ใบส่งของที่เกิดขึ้นอัตโนมัติจองสต็อก (Reserved/Assigned) ได้ทันทีจากสต็อกส่วนเกินที่เหลือ โดยไม่ต้องเปิด "Produce FG" เลย — ตัวอย่างจริง: S00128</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>✨ พฤติกรรมจริงที่พบ: ลิงก์ "Produce FG" ยังปรากฏอยู่บนบรรทัดเสมอ ไม่ว่าสต็อกจะพอหรือไม่ — จุดต่างจริงของ G2a คือ "ไม่จำเป็นต้องกด" เพราะใบส่งของจองสต็อกสำเร็จได้เองทันที ไม่ใช่ว่าลิงก์หายไป</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-08</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>จัดส่งใบส่งของของบรรทัดที่สอง (SO2)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-07 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบส่งของ (Delivery) ที่เกิดขึ้นอัตโนมัติของ S00128
+2. กดปุ่ม Validate</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>ใบส่งของเปลี่ยนสถานะเป็น Done สำเร็จทันที เหมือนกับ TC-E2E-M5-06 ทุกประการ — ตัวอย่างจริง: EG01/OUT/00082</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -925,7 +1233,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G2b. ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง) — ย้าย Slab เข้าสถานีผลิต แล้วเปิด wizard "Produce FG" ตัด/ผลิตจริง</t>
+          <t>G4. บัญชี (Accounting + Payment) — ออกใบแจ้งหนี้ทั้ง 2 ใบ + รับชำระเงิน + ตรวจรายการบัญชี (COGS ต้องไม่เป็น 0)</t>
         </is>
       </c>
     </row>
@@ -994,22 +1302,24 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-04</t>
+          <t>TC-E2E-M5-09</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>เห็นคิวงานที่หน้า Factory Worklist</t>
+          <t>ออกใบแจ้งหนี้บรรทัดแรก (SO1)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-02 เสร็จแล้ว (กรณีสต็อกไม่พอ)</t>
+          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดเมนู Stone Slab &gt; Tools &gt; Factory Worklist</t>
+          <t>1. เปิด Sale Order S00127 &gt; กดปุ่ม "Create Invoice"
+2. เลือก "Regular Invoice" &gt; Create Draft Invoice
+3. กด Confirm บนใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1019,12 +1329,12 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เห็นแถวของ SO นี้ขึ้นคิวงาน คอลัมน์ "ต้องทำ" ระบุ "รอผลิต FG (Cut to Order / Produce FG)" — ตัวอย่างจริง: S00112, สินค้า Carrara White - Countertop, จำนวน 3.00</t>
+          <t>ใบแจ้งหนี้ยืนยันสำเร็จ สถานะ Posted ยอดรวม 9,095.00 บาท (รวม VAT) — ตัวอย่างจริง: INV/2026/00031</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H4" s="7" t="n"/>
@@ -1036,36 +1346,34 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-05</t>
+          <t>TC-E2E-M5-10</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ย้าย Slab (วัตถุดิบของ FG) เข้าสถานีผลิต</t>
+          <t>ออกใบแจ้งหนี้บรรทัดที่สอง (SO2)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>มี Slab ของ Material เดียวกับ FG นี้ อยู่ที่ Location "Stone Available"</t>
+          <t>ทำ TC-E2E-M5-08 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Inventory &gt; Internal Transfers &gt; New
-2. ตั้งต้นทาง (Source Location) = Stone Available
-3. ตั้งปลายทาง (Destination Location) = Stone Production
-4. เพิ่มสินค้า Slab ของ Material นั้น จำนวน 1
-5. กด Validate</t>
+          <t>1. เปิด Sale Order S00128 &gt; กดปุ่ม "Create Invoice"
+2. เลือก "Regular Invoice" &gt; Create Draft Invoice
+3. กด Confirm บนใบแจ้งหนี้</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>สินค้า = "Carrara White - Slab" จำนวน = 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ใบโอนย้ายเปลี่ยนสถานะเป็น Done Slab ถูกย้ายเข้า Stone Production เรียบร้อย พร้อมให้ผลิตต่อ — ตัวอย่างจริง: EG01/INT/00053 (Slab BDL-00002 #8)</t>
+          <t>ใบแจ้งหนี้ยืนยันสำเร็จ สถานะ Posted ยอดรวม 9,095.00 บาทเท่ากับใบแรกทุกประการ (ราคาขายเท่ากัน) — ตัวอย่างจริง: INV/2026/00032</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1082,23 +1390,22 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-06</t>
+          <t>TC-E2E-M5-11</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>เปิด wizard "Produce FG" — ระบบจับคู่ Slab ให้อัตโนมัติ</t>
+          <t>ตรวจรายการบัญชีของใบแจ้งหนี้ (Journal Items) — ต้นทุนขาย (COGS) ต้องไม่เป็น 0</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-05 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-09 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. กลับไปที่บรรทัดสินค้า FG ใน Sale Order
-2. กดปุ่ม "Produce FG"</t>
+          <t>1. เปิด Customer Invoice &gt; กดแท็บ "Journal Items"</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1108,7 +1415,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>หน้าต่าง Produce FG เปิดขึ้น ช่อง "Slab to Consume" ถูกเติมชื่อ Slab ที่เพิ่งย้ายเข้าสถานีผลิตให้อัตโนมัติ (ไม่ต้องเลือกเอง) พร้อมบรรทัดผลผลิต 1 บรรทัดตรงกับสินค้าที่ขายอยู่แล้ว — ตัวอย่างจริง: Slab to Consume = BDL-00002 #8</t>
+          <t>เห็นรายการครบ 5 บรรทัด สมดุลกันทั้ง 2 ฝั่ง (เดบิต = เครดิต) พร้อม Analytic Distribution ผูกกับ Material/Block ทุกบรรทัด — ตัวอย่างจริง INV/2026/00031: เครดิต "411150 Sales Revenue - FG Production" 8,500.00, เครดิต "213200 Output VAT" 595.00, เดบิต "112100 Trade Receivables" 9,095.00, เครดิต "113150 Inventory - Stone FG (Finished Goods)" 375.00, เดบิต "511100 Cost of Goods Sold" 375.00 — รวมสมดุล 9,470.00 = 9,470.00 (COGS ไม่ใช่ 0 บาท ตัดจริงตามบัญชีที่ถูกต้อง)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1125,45 +1432,41 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-07</t>
+          <t>TC-E2E-M5-12</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>กรอกจำนวนผลผลิตจริงจาก Slab นี้ แล้วกดผลิต</t>
+          <t>บันทึกรับชำระเงินใบแจ้งหนี้บรรทัดแรก (SO1)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-09 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. แก้จำนวนในบรรทัดผลผลิตเป็นจำนวนที่ตัด/ผลิตได้จริงจาก Slab นี้
-2. กดปุ่ม "Produce"</t>
+          <t>1. เปิดใบแจ้งหนี้ &gt; กดปุ่ม "Pay"
+2. เลือกวิธีชำระเงินที่ต้องการ &gt; กดยืนยัน</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>จำนวนผลผลิต = 6 (ลูกค้าสั่งแค่ 3 — ตัดเผื่อสต็อกไว้ขายรอบหน้าด้วย)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>เกิดใบสั่งผลิต (Manufacturing Order) ใหม่ ผูก Slab ที่เลือกเป็นวัตถุดิบ จำนวนที่ต้องผลิตตรงกับที่กรอก — ตัวอย่างจริง: EG01/STFG/00012 (To Produce 6.00)</t>
+          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" ทันที — ตัวอย่างจริง: INV/2026/00031</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>1 Slab ตัดออกมาได้กี่ชิ้นไม่ตายตัว — ฝ่ายผลิตกรอกจำนวนจริงที่ตัดได้ตอนนี้เอง ไม่ต้องเท่ากับจำนวนที่ลูกค้าสั่งพอดี (ตัดเผื่อสต็อกไว้ขายออเดอร์ถัดไปได้)</t>
-        </is>
-      </c>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
@@ -1172,23 +1475,23 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-08</t>
+          <t>TC-E2E-M5-13</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>กด "Complete FG Production" — ปิดงานผลิต</t>
+          <t>บันทึกรับชำระเงินใบแจ้งหนี้บรรทัดที่สอง (SO2)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-07 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-10 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดใบสั่งผลิตที่เพิ่งสร้าง
-2. กดปุ่ม "Complete FG Production"</t>
+          <t>1. เปิดใบแจ้งหนี้ &gt; กดปุ่ม "Pay"
+2. เลือกวิธีชำระเงินที่ต้องการ &gt; กดยืนยัน</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1198,12 +1501,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>ใบสั่งผลิตเปลี่ยนสถานะเป็น Done Slab ที่ใช้ถูกตัดออกจากสต็อกจนหมด (ใช้ครั้งเดียว ไม่เหลือให้ใช้ซ้ำ) FG เข้าสต็อกจริงตามจำนวนที่ผลิต พร้อม Lot ใหม่ — ตัวอย่างจริง: EG01/STFG/00012 ผลิตสำเร็จ 6.00/6.00 ได้ Lot "FG-EG01/STFG/00012"</t>
+          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" ทันทีเหมือนกัน — ตัวอย่างจริง: INV/2026/00032</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H8" s="7" t="n"/>
@@ -1211,384 +1514,6 @@
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
       <c r="L8" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>G3. จัดส่ง (Delivery) — ทั้ง 2 กรณี (ผลิตใหม่ / มีสต็อกอยู่แล้ว) ส่งมอบแบบเดียวกัน ไม่มีการดักสแกน Serial</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>TC ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-09</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>ส่งมอบสินค้าที่เพิ่งผลิตเสร็จ (กรณี G2b)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-08 เสร็จแล้ว มีใบส่งของอัตโนมัติรออยู่ตั้งแต่ตอน Confirm</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิด Inventory &gt; Deliveries
-2. เปิดใบส่งของของ SO นี้
-3. กด Validate</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>ใบส่งของเปลี่ยนสถานะเป็น Done — ไม่มีการดักสแกน Serial เหมือนสินค้า Block/Slab (ส่งได้ทันทีเมื่อสต็อกพร้อม) — ตัวอย่างจริง: EG01/OUT/00066 (Carrara White - Countertop 3.00/3.00 พร้อมส่ง)</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-10</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ส่งมอบสินค้าที่ไม่ต้องผลิต (กรณี G2a)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-03 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิด Inventory &gt; Deliveries
-2. เปิดใบส่งของของ SO นี้
-3. กด Validate</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>ใบส่งของเปลี่ยนสถานะเป็น Done ทันที ดึงสต็อกจาก FG ที่มีอยู่แล้วโดยไม่ผ่านขั้นตอนผลิตเลยสักครั้ง — ตัวอย่างจริง: EG01/OUT/00067 (Carrara White - Countertop 2.00/2.00)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>G4. บัญชี (Accounting) — ออกใบแจ้งหนี้ &amp; ตรวจรายการบัญชี</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>TC ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-11</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>ออกใบแจ้งหนี้และยืนยัน (Post)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-09 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิด Sale Order &gt; กด "Create Invoice"
-2. เลือก "Regular invoice" &gt; กด "Create Draft Invoice"
-3. เปิดใบแจ้งหนี้ที่เกิดขึ้น &gt; กด Confirm</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>ใบแจ้งหนี้สถานะ Posted ยอดตรงกับ SO เป๊ะ — ตัวอย่างจริง: INV/2026/00018 (48,150.00 บาท จาก S00112)</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-12</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ตรวจรายการบัญชีของใบแจ้งหนี้ (Journal Items) — ยืนยันว่าลง COGS ถูกต้อง</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-11 เสร็จแล้ว (ตัวอย่างนี้ใช้ SO/Invoice อีกใบที่ขายจาก FG ล็อตใหม่ล้วน เพื่อให้เห็นรายการ COGS จริง)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิดใบแจ้งหนี้ &gt; กดแท็บ "Journal Items"</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>เดบิต/เครดิตสมดุลกัน (รวมเท่ากันทั้ง 2 ฝั่ง) พร้อมมีรายการ COGS ปรากฏครบ — ตัวอย่างจริง: INV/2026/00020 (SO S00114, ขาย FG ล็อตใหม่ 2 หน่วย) เดบิต Trade Receivables 32,100.00 = เครดิต Sales Revenue - FG Production 30,000.00 + Output VAT 2,100.00 บาท และมีคู่ COGS แยกสมดุลกันเอง: เดบิต 511100 Cost of Goods Sold 933.33 = เครดิต 113150 Inventory - Stone FG 933.33 บาท (933.33 = 466.67 บาท/หน่วย × 2 หน่วย ตรงกับต้นทุน Slab จริงเป๊ะ)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>ℹ️ หมายเหตุ: ใบแจ้งหนี้ของ S00112/S00113 เองไม่มีรายการ COGS ขึ้นมา — ตอนแรกเข้าใจผิดว่าเป็นบั๊ก แต่ตรวจสอบลึกแล้วพบว่าไม่ใช่: หินที่ส่งมอบ 5 หน่วยในนั้นตรงกับสต็อกเก่าที่มีอยู่แล้ว 5 หน่วยพอดี ซึ่งเป็นข้อมูลสาธิตเก่าที่มีมูลค่าบันทึกไว้ 0.00 บาทตั้งแต่ต้น (ช่องว่างข้อมูลที่รู้และยอมรับไว้แล้วก่อนหน้านี้ ไม่ใช่ปัญหาใหม่) ระบบคิดต้นทุนแบบ FIFO จึงตัดจากของเก่า (มูลค่า 0) ก่อนของใหม่ที่เพิ่งผลิตถูกต้องแล้วตามหลัก FIFO — ไม่ใช่บั๊กของ Mode 5 เลย ดูตัวอย่างที่ยืนยันว่าระบบลงบัญชีถูกต้องจริงด้านล่าง (ใช้ของใหม่ล้วน ไม่ปนของเก่า)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode5.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode5.xlsx
@@ -11,7 +11,6 @@
     <sheet name="G1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="G2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="G3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="G4" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:D12"/>
+  <dimension ref="C2:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="2" max="2"/>
@@ -470,7 +469,7 @@
     <row r="2">
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>EMG-O — Test Cases: E2E Flow — Mode 5 (Stone Production / FG Production)</t>
+          <t>EMG-O — Test Cases: E2E Flow — Mode 5 (Slab → Finished Goods)</t>
         </is>
       </c>
     </row>
@@ -491,7 +490,7 @@
     <row r="6">
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>High / Medium / Low: 10 / 3 / 0</t>
+          <t>High / Medium / Low: 11 / 2 / 0</t>
         </is>
       </c>
     </row>
@@ -510,41 +509,31 @@
     <row r="9">
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G1 — ขาย (Sale — สินค้าสำเร็จรูปที่ต้องผลิตจาก Slab)</t>
+          <t>G1 — เตรียมแผ่น (Slab) ก่อนผลิต — เหมือน Mode 3 ทุกประการ</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>G2 — ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง)</t>
+          <t>G2 — ขาย + ผลิต — สินค้า FG มาตรฐาน (Standard, เช่น Countertop)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G3 — จัดส่ง + ขายซ้ำ — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ)</t>
+          <t>G3 — ขาย + ผลิต — งาน Custom สั่งทำพิเศษ (ADR-068, เช่น เจดีย์บัว/ซุ้มบัว)</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>G4 — บัญชี (Accounting + Payment)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -558,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -578,7 +567,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G1. ขาย (Sale — สินค้าสำเร็จรูปที่ต้องผลิตจาก Slab) — ADR-029 — ขายสินค้า FG (เช่น Countertop) ที่ยังไม่ได้ผลิตจริงได้เลย</t>
+          <t>G1. เตรียมแผ่น (Slab) ก่อนผลิต — เหมือน Mode 3 ทุกประการ — ตัด Block เป็น Slab ล่วงหน้า ก่อนขายจริง — reuse กลไกเดียวกับ Mode 3 (Block-to-Slab) ไม่มีอะไรใหม่</t>
         </is>
       </c>
     </row>
@@ -652,30 +641,31 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>เพิ่มบรรทัดสินค้า FG (Finished Good) ใน Sale Order ใหม่</t>
+          <t>ตัด Block เป็น Slab ไว้ล่วงหน้า (ยังไม่ผูกกับ SO ใดๆ)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>มี Slab พร้อมอยู่แล้วในสต็อกที่สถานีผลิต (Stone Production) จาก Material ที่ตั้งค่า FG ไว้ (มี Block/Slab/FG ครบ 3 สินค้า)</t>
+          <t>มี Block พร้อมอยู่แล้วในสต็อก (ยังไม่ตัด) จาก Material ที่ตั้งค่า Finished Good ไว้ครบ (มี Block/Slab/FG 3 สินค้า)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Sales &gt; Orders &gt; New
-2. เลือกลูกค้า
-3. เพิ่มบรรทัด เลือกสินค้า FG ของ Material นั้น</t>
+          <t>1. เปิด Manufacturing &gt; New
+2. เลือก Block ที่ต้องการตัด + กรอกขนาดที่ต้องการ
+3. ย้ายด่วน (Move to Production) &gt; Confirm &gt; ทำ Work Orders &gt; Complete Cut</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
-สินค้า = E2E Mode5 Fresh Test - Countertop</t>
+          <t>Stone Block = BLK-26-0036
+Target Slab L (M) = 1.50
+Target Slab H (M) = 1.00</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เพิ่มบรรทัดสำเร็จ ราคาต่อหน่วยขึ้นเป็นราคาตั้งต้นของสินค้า FG (ตัวอย่างจริง: 8,500/หน่วย)</t>
+          <t>ได้แผ่นหินจริง 1 แผ่นเข้าสต็อก (ตัวอย่างจริง: BLK-26-0036 #1, 1.50 ตร.ม.) Block เหลือ CBM ส่วนที่ยังไม่ตัดไว้ขายต่อได้ (ตัวอย่างจริง: เหลือ 2.97 CBM จาก 3.00)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -683,53 +673,15 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>ใช้กลไกเดียวกับ Mode 3 (Block-to-Slab) เป๊ะๆ — Mode 5 ไม่มีขั้นตอนตัดของตัวเอง ต้องมี Slab พร้อมอยู่ในสต็อกก่อนเสมอ</t>
+        </is>
+      </c>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-02</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ยืนยัน (Confirm) Sale Order — ยังไม่มี FG ในสต็อกเลย</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-01 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>1. กดปุ่ม Confirm บน Sale Order</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>SO เปลี่ยนสถานะเป็น Sales Order ยอดรวม 9,095.00 บาท (รวม VAT) — บรรทัดสินค้า FG ปรากฏลิงก์ "Produce FG" ให้กดเพื่อผลิต เพราะยังไม่มีสต็อก FG เลย — ตัวอย่างจริง: S00127</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -745,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -765,7 +717,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G2. ผลิต — กรณี FG ไม่มี/ไม่พอในสต็อก (ต้องผลิตจริง) — ADR-029, stone.fg.production.wizard — เปิด wizard "Produce FG" ตัดจาก Slab ที่มีอยู่</t>
+          <t>G2. ขาย + ผลิต — สินค้า FG มาตรฐาน (Standard, เช่น Countertop) — ADR-029/067 — Produce FG สร้าง MO ตรงเลย ไม่ผ่าน wizard แล้ว</t>
         </is>
       </c>
     </row>
@@ -834,32 +786,36 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-03</t>
+          <t>TC-E2E-M5-02</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>เปิด wizard "Produce FG" — ระบบจับคู่ Slab ที่จะใช้ให้อัตโนมัติ</t>
+          <t>เพิ่มบรรทัดสินค้า FG มาตรฐานใน Sale Order แล้ว Confirm</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-02 เสร็จแล้ว มี Slab พร้อมอยู่ที่สถานีผลิตแล้ว (ย้ายด้วย Internal Transfer ล่วงหน้า)</t>
+          <t>มี Slab พร้อมอยู่แล้วในสต็อกจาก TC-E2E-M5-01</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. กดลิงก์ "Produce FG" บนบรรทัดสินค้า FG ของ Sale Order</t>
+          <t>1. เปิด Sales &gt; Orders &gt; New
+2. เลือกลูกค้า
+3. เพิ่มบรรทัด เลือกสินค้า FG มาตรฐาน
+4. กด Confirm</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
+สินค้า = E2E Mode5 Fresh Test V2 - Countertop</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>เปิด wizard สำเร็จ ช่อง "Slab to Consume" เติมให้อัตโนมัติเป็น Slab ตัวแรกที่มี Material ตรงกันและสถานะ Available (v1: จับคู่ตาม Material อย่างเดียว) พร้อมบรรทัดผลผลิตเริ่มต้น 1 บรรทัดตรงกับสินค้าที่ขาย จำนวน 1 — ตัวอย่างจริง: Slab BLK-26-0029 #1</t>
+          <t>SO ยืนยันสำเร็จ ยอดรวม 9,630.00 บาท (รวม VAT) บรรทัดสินค้า FG ปรากฏลิงก์ "Produce FG" เพราะยังไม่มีสต็อก FG เลย — ตัวอย่างจริง: S00137</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -876,33 +832,32 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-04</t>
+          <t>TC-E2E-M5-03</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ปรับจำนวนผลผลิตแล้วกด "Produce" — สร้าง Manufacturing Order</t>
+          <t>กดลิงก์ "Produce FG" — ระบบสร้าง Manufacturing Order ตรงทันที ไม่มี wizard popup แล้ว</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-03 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-02 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. แก้ไขจำนวนในบรรทัดผลผลิตจาก 1 เป็น 2
-2. กดปุ่ม "Produce"</t>
+          <t>1. กดลิงก์ "Produce FG" บนบรรทัดสินค้า FG ของ Sale Order</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>จำนวนผลผลิต = 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>สร้าง Manufacturing Order สำเร็จ ยืนยันอัตโนมัติทันที (Confirmed) ระบบเติม Bill of Material ให้อัตโนมัติจาก FG Material ที่เลือก จำนวนที่จะผลิต = 2.00 Slab ที่เลือกถูกจับจองเป็นวัตถุดิบ (To Consume 1.00, Available) ผูกกับบรรทัด SO เดิม ("For Sale Order Line") — ตัวอย่างจริง: EG01/STFG/00015</t>
+          <t>เปิดหน้า Manufacturing Order ฉบับร่างทันที (ไม่ใช่ popup) ช่อง Slab ที่ใช้ผลิตเติมให้อัตโนมัติเป็นแผ่นที่มี Material ตรงกันและสถานะ Available — ตัวอย่างจริง: MO EG01/STFG/00022, Slab BLK-26-0036 #1, ผูกกับ "For Sale Order Line" = S00137 ให้อัตโนมัติ</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -912,7 +867,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>ผลผลิตต่อ Slab กำหนดตอนผลิตจริง ไม่ใช่อัตราตายตัว (ADR-029) — เคสนี้ตั้งใจผลิต 2 หน่วยจาก Slab เดียว แม้บรรทัด SO ต้องการแค่ 1 หน่วย เพื่อเผื่อสต็อกไว้ขายลูกค้ารายถัดไป (ดู TC-E2E-M5-07)</t>
+          <t>✨ กลไกใหม่ (ADR-067, 14 ก.ย. 2026): เดิมกดแล้วเด้ง wizard ให้เลือก Slab/จำนวน ตอนนี้กดแล้วได้ MO ฉบับร่างเปิดขึ้นมาเลย ระบบจับคู่ Slab ที่ Material ตรงกันให้อัตโนมัติ ไม่ต้องเลือกเองก็ได้</t>
         </is>
       </c>
       <c r="I5" s="7" t="n"/>
@@ -923,22 +878,23 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-05</t>
+          <t>TC-E2E-M5-04</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>กด "Complete FG Production" — ได้สินค้า FG จริงเข้าสต็อก</t>
+          <t>ย้ายด่วน (Move to Production) แล้ว Confirm Manufacturing Order</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-04 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-03 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. กดปุ่ม "Complete FG Production" บน Manufacturing Order</t>
+          <t>1. กดปุ่ม "ย้ายด่วน (Move to Production)" บน MO
+2. กดปุ่ม Confirm</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -948,7 +904,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Manufacturing Order เสร็จสมบูรณ์ (สถานะ Done) จำนวนที่ผลิตจริง = 2.00/2.00 ได้ Lot/Serial ใหม่ของสินค้า FG (ตัวอย่างจริง: FG-EG01/STFG/00015) Slab ที่ใช้เป็นวัตถุดิบเปลี่ยนสถานะเป็น Consumed หมดสภาพขายต่อ สินค้า FG 2 หน่วยเข้าสต็อกจริง</t>
+          <t>Slab ถูกย้ายไปสถานีผลิต (Stone Production) สำเร็จ แล้ว Confirm ผ่านทันที ไม่มี error — สถานะ MO เปลี่ยนเป็น Confirmed</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -961,6 +917,139 @@
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
       <c r="L6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-05</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ทำ Work Order ให้เสร็จ แล้วบันทึกขนาดจริงในแท็บ "FG Output"</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-04 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1. ไปแท็บ "Work Orders" กดเริ่ม/เสร็จตามลำดับจนครบ
+2. ไปแท็บ "FG Output" เพิ่มแถวขนาดจริงที่ตัดได้</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Width = 1.48, Length = 0.98, Thickness = 0.02, Qty = 1</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Work Orders ขึ้น Finished ครบ MO เปลี่ยนสถานะเป็น "To Close" แท็บ FG Output มี 1 แถวตามที่กรอก</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>✨ กลไกใหม่ (ADR-067): แท็บนี้แทนที่ wizard เดิมทั้งหมด — Factory กรอกขนาด/จำนวนที่ตัดได้จริงหลังตัดเสร็จ ตรงกับใบรายงานตัดกระดาษของโรงงานเป๊ะ ไม่มีคอลัมน์สินค้าเพราะทุกแถวนับรวมเป็นสินค้า FG ตัวเดียวของ MO นี้อยู่แล้ว</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>กด "Complete FG Production" — ได้สินค้า FG จริงเข้าสต็อก</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-05 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1. กดปุ่ม "Complete FG Production" บน Manufacturing Order</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>MO เสร็จสมบูรณ์ (สถานะ Done) ได้ Lot/Serial ใหม่ของสินค้า FG (ตัวอย่างจริง: FG-EG01/STFG/00022) Slab ที่ใช้เป็นวัตถุดิบเปลี่ยนสถานะเป็น Consumed สินค้า FG 1 หน่วยเข้าสต็อกจริง</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-07</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>จัดส่ง ออกใบแจ้งหนี้ และรับชำระเงิน (Standard)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบส่งของที่เกิดขึ้นอัตโนมัติ &gt; Validate
+2. เปิด SO &gt; Create Invoice &gt; Regular Invoice &gt; Confirm
+3. เปิดใบแจ้งหนี้ &gt; Pay &gt; ยืนยันการชำระ</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>ใบส่งของ Done (ตัวอย่างจริง: EG01/OUT/00091) ใบแจ้งหนี้ Posted ยอด 9,630.00 (ตัวอย่างจริง: INV/2026/00037) แล้วขึ้น In Payment — Journal Items 5 บรรทัด สมดุล 10,110.00 = 10,110.00 (COGS 480.00 ไม่ใช่ 0)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -976,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -996,7 +1085,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>G3. จัดส่ง + ขายซ้ำ — กรณี FG มีสต็อกพอแล้ว (ไม่ต้องผลิตซ้ำ) — ส่งของบรรทัดแรก แล้วขายลูกค้าใหม่ด้วยสต็อกส่วนเกินที่เหลือ ไม่ต้องผ่าน wizard อีก</t>
+          <t>G3. ขาย + ผลิต — งาน Custom สั่งทำพิเศษ (ADR-068, เช่น เจดีย์บัว/ซุ้มบัว) — ใหม่ทั้งหมด session นี้ — Stage 2 (ถอดแบบ) + Stage 3 (ประกอบ) สำหรับงานที่ไม่มี BOM ตายตัว</t>
         </is>
       </c>
     </row>
@@ -1065,33 +1154,38 @@
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-06</t>
+          <t>TC-E2E-M5-08</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>จัดส่งใบส่งของของบรรทัดแรก (SO1)</t>
+          <t>Stage 2 — สร้าง "Cutting Plan" MO ถอดแบบ Slab เป็นชิ้นย่อย</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-05 เสร็จแล้ว มีสินค้า FG พร้อมส่งแล้ว</t>
+          <t>มี Slab พร้อมอยู่แล้วในสต็อก (แยกจาก Slab ที่ใช้ใน G2)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดใบส่งของ (Delivery) ที่เกิดขึ้นอัตโนมัติของ S00127
-2. กดปุ่ม Validate</t>
+          <t>1. เปิด Manufacturing &gt; New
+2. เลือก "Source Slab (Cutting Plan)" เป็น Slab ที่จะถอดแบบ
+3. ไปแท็บ "Planned/Actual Pieces" เพิ่มแถวขนาดชิ้นที่ต้องการ
+4. ย้ายด่วน &gt; Confirm &gt; Work Orders &gt; "Complete Cutting Plan"</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Source Slab = BLK-26-0036 #2
+ชิ้นที่ 1: 0.25 x 0.20 m
+ชิ้นที่ 2: 0.20 x 0.15 m
+ชิ้นที่ 3: 0.15 x 0.10 m</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>ใบส่งของเปลี่ยนสถานะเป็น Done สำเร็จทันที (จองสต็อกไว้ให้แล้วตั้งแต่ผลิตเสร็จ) — ตัวอย่างจริง: EG01/OUT/00081</t>
+          <t>MO เสร็จสมบูรณ์ (ตัวอย่างจริง: EG01/STCPL/00009) ได้ชิ้นงานจริง 3 ชิ้้น สถานะ "Staged (Cutting Plan WIP)" ทุกชิ้น — แชร์ Lot เดียวกันทั้งหมด (ตัวอย่างจริง: CUT-EG01/STCPL/00009, รวม 3.00 หน่วย) ชิ้นเหล่านี้จะไม่โผล่ในหน้า "Select Slabs" ของโหมดขายอื่นเลย เพราะยังไม่ใช่สต็อกขายได้จริง</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1099,7 +1193,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>✨ กลไกใหม่ทั้งหมด (ADR-068, session นี้): ใช้เมื่องานสั่งทำไม่มีสินค้า FG มาตรฐานให้เลือก ต้องเอา Slab มา "ถอดแบบ" เป็นชิ้นเล็กๆ ก่อน ทุกชิ้นจาก MO เดียวกันจะแชร์ Lot เดียวกัน (กันของปนกันตอนขนย้าย ไม่ใช่ QC รายชิ้น)</t>
+        </is>
+      </c>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
       <c r="K4" s="7" t="n"/>
@@ -1108,272 +1206,36 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-07</t>
+          <t>TC-E2E-M5-09</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>สร้าง Sale Order ใหม่ขายสินค้า FG ตัวเดียวกันอีกครั้ง — ใช้สต็อกส่วนเกิน</t>
+          <t>สร้าง Sale Order ขายสินค้า Custom (ไม่มี FG มาตรฐานให้เลือก)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว มีสินค้า FG เหลือในสต็อก 1 หน่วยจากการผลิตครั้งก่อน</t>
+          <t>ทำ TC-E2E-M5-08 เสร็จแล้ว มี BOQ Document ผูกกับ Sale Order นี้ไว้ (จำเป็นสำหรับ wizard สร้าง BOM ในขั้นถัดไป)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Sales &gt; Orders &gt; New
-2. เลือกลูกค้าเดิม
-3. เพิ่มบรรทัด เลือกสินค้า FG ตัวเดียวกัน จำนวน 1
+          <t>1. เปิด Sales &gt; Orders &gt; New (ผูก BOQ Document)
+2. เลือกลูกค้า
+3. เพิ่มบรรทัด เลือกสินค้า Custom
 4. กด Confirm</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
-สินค้า = E2E Mode5 Fresh Test - Countertop
-จำนวน = 1</t>
+สินค้า = เจดีย์บัว S (Custom)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>SO ยืนยันสำเร็จ ยอดรวม 9,095.00 บาทเท่าเดิม ใบส่งของที่เกิดขึ้นอัตโนมัติจองสต็อก (Reserved/Assigned) ได้ทันทีจากสต็อกส่วนเกินที่เหลือ โดยไม่ต้องเปิด "Produce FG" เลย — ตัวอย่างจริง: S00128</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>✨ พฤติกรรมจริงที่พบ: ลิงก์ "Produce FG" ยังปรากฏอยู่บนบรรทัดเสมอ ไม่ว่าสต็อกจะพอหรือไม่ — จุดต่างจริงของ G2a คือ "ไม่จำเป็นต้องกด" เพราะใบส่งของจองสต็อกสำเร็จได้เองทันที ไม่ใช่ว่าลิงก์หายไป</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-08</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>จัดส่งใบส่งของของบรรทัดที่สอง (SO2)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-07 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิดใบส่งของ (Delivery) ที่เกิดขึ้นอัตโนมัติของ S00128
-2. กดปุ่ม Validate</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>ใบส่งของเปลี่ยนสถานะเป็น Done สำเร็จทันที เหมือนกับ TC-E2E-M5-06 ทุกประการ — ตัวอย่างจริง: EG01/OUT/00082</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>G4. บัญชี (Accounting + Payment) — ออกใบแจ้งหนี้ทั้ง 2 ใบ + รับชำระเงิน + ตรวจรายการบัญชี (COGS ต้องไม่เป็น 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>TC ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Status (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>Tester</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-09</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>ออกใบแจ้งหนี้บรรทัดแรก (SO1)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-06 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิด Sale Order S00127 &gt; กดปุ่ม "Create Invoice"
-2. เลือก "Regular Invoice" &gt; Create Draft Invoice
-3. กด Confirm บนใบแจ้งหนี้</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>ใบแจ้งหนี้ยืนยันสำเร็จ สถานะ Posted ยอดรวม 9,095.00 บาท (รวม VAT) — ตัวอย่างจริง: INV/2026/00031</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>TC-E2E-M5-10</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ออกใบแจ้งหนี้บรรทัดที่สอง (SO2)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>ทำ TC-E2E-M5-08 เสร็จแล้ว</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>1. เปิด Sale Order S00128 &gt; กดปุ่ม "Create Invoice"
-2. เลือก "Regular Invoice" &gt; Create Draft Invoice
-3. กด Confirm บนใบแจ้งหนี้</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>ใบแจ้งหนี้ยืนยันสำเร็จ สถานะ Posted ยอดรวม 9,095.00 บาทเท่ากับใบแรกทุกประการ (ราคาขายเท่ากัน) — ตัวอย่างจริง: INV/2026/00032</t>
+          <t>SO ยืนยันสำเร็จ ยอดรวม 12,840.00 บาท (รวม VAT) บรรทัดสินค้าปรากฏลิงก์ "Produce FG" เหมือนเดิม แต่จะพาไปหน้าต่าง "สร้าง BOM จาก BOQ" แทน (ไม่ใช่สร้าง MO ตรงแบบ G2) เพราะสินค้านี้ไม่มี FG Raw Material ตายตัว — ตัวอย่างจริง: S00138</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1390,12 +1252,12 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-11</t>
+          <t>TC-E2E-M5-10</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ตรวจรายการบัญชีของใบแจ้งหนี้ (Journal Items) — ต้นทุนขาย (COGS) ต้องไม่เป็น 0</t>
+          <t>Stage 3 — กด "Produce FG" เปิด wizard "สร้าง BOM จาก BOQ" เลือก Cutting Plan Lot</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1405,17 +1267,19 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. เปิด Customer Invoice &gt; กดแท็บ "Journal Items"</t>
+          <t>1. กดลิงก์ "Produce FG" บนบรรทัดสินค้า
+2. เลือกช่อง "Cutting Plan Lot (Stage 2)" เป็น Lot จาก Stage 2
+3. กด "สร้าง BOM + MO"</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cutting Plan Lot (Stage 2) = CUT-EG01/STCPL/00009</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>เห็นรายการครบ 5 บรรทัด สมดุลกันทั้ง 2 ฝั่ง (เดบิต = เครดิต) พร้อม Analytic Distribution ผูกกับ Material/Block ทุกบรรทัด — ตัวอย่างจริง INV/2026/00031: เครดิต "411150 Sales Revenue - FG Production" 8,500.00, เครดิต "213200 Output VAT" 595.00, เดบิต "112100 Trade Receivables" 9,095.00, เครดิต "113150 Inventory - Stone FG (Finished Goods)" 375.00, เดบิต "511100 Cost of Goods Sold" 375.00 — รวมสมดุล 9,470.00 = 9,470.00 (COGS ไม่ใช่ 0 บาท ตัดจริงตามบัญชีที่ถูกต้อง)</t>
+          <t>สร้าง BOM + Manufacturing Order สำเร็จ แต่ MO ยังอยู่สถานะ Draft ให้ตรวจสอบก่อน (ต่างจากงาน Custom ที่ไม่ใช้ Cutting Plan Lot ซึ่งจะ Confirm ให้อัตโนมัติทันที) — ตัวอย่างจริง: EG01/STFG/00023 มีปุ่ม "Cutting Plan MO" เชื่อมกลับไปหา MO ของ Stage 2 ให้แล้ว</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1423,7 +1287,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>✨ ส่วนขยายใหม่ของ wizard เดิม (ADR-064 เดิม + ADR-068 เพิ่มเข้ามา): นอกจากเลือกวัสดุจาก BOQ ได้เหมือนเดิม ตอนนี้เลือก "Cutting Plan Lot (Stage 2)" ได้ด้วย — ระบบดึงมาทั้งก้อน (จำนวนเต็มของ Lot นั้น) ไม่ต้องกรอกจำนวนเอง</t>
+        </is>
+      </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
@@ -1432,23 +1300,23 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-12</t>
+          <t>TC-E2E-M5-11</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>บันทึกรับชำระเงินใบแจ้งหนี้บรรทัดแรก (SO1)</t>
+          <t>Confirm MO Stage 3 — ระบบเติมวัตถุดิบจาก Lot ให้อัตโนมัติ</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-09 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-10 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดใบแจ้งหนี้ &gt; กดปุ่ม "Pay"
-2. เลือกวิธีชำระเงินที่ต้องการ &gt; กดยืนยัน</t>
+          <t>1. ตรวจแท็บ "Components" ก่อน Confirm
+2. กดปุ่ม Confirm</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1458,12 +1326,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" ทันที — ตัวอย่างจริง: INV/2026/00031</t>
+          <t>แท็บ Components เติมแถววัตถุดิบจาก Cutting Plan Lot ให้อัตโนมัติ จำนวนเท่ากับที่มีอยู่เต็มก้อน (ตัวอย่างจริง: E2E Mode5 Fresh Test V2 - Cutting Plan WIP, 3.00 หน่วย) Confirm ผ่านสำเร็จ ไม่ต้องกรอกอะไรเพิ่มเอง</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -1475,23 +1343,22 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>TC-E2E-M5-13</t>
+          <t>TC-E2E-M5-12</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>บันทึกรับชำระเงินใบแจ้งหนี้บรรทัดที่สอง (SO2)</t>
+          <t>ทำ MO ให้เสร็จด้วยปุ่ม Produce มาตรฐานของ Odoo (ไม่มีปุ่มเฉพาะ)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M5-10 เสร็จแล้ว</t>
+          <t>ทำ TC-E2E-M5-11 เสร็จแล้ว</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1. เปิดใบแจ้งหนี้ &gt; กดปุ่ม "Pay"
-2. เลือกวิธีชำระเงินที่ต้องการ &gt; กดยืนยัน</t>
+          <t>1. กรอกจำนวนที่ผลิตจริง &gt; กด Generate Lot ถ้ายังไม่มี &gt; กดปุ่ม Produce All</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1501,19 +1368,67 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" ทันทีเหมือนกัน — ตัวอย่างจริง: INV/2026/00032</t>
+          <t>MO เสร็จสมบูรณ์ (สถานะ Done) ได้สินค้า Custom 1 หน่วยเข้าสต็อกจริง ชิ้นงานทั้ง 3 ชิ้นจาก Stage 2 เปลี่ยนสถานะจาก "Staged" เป็น "Consumed" อัตโนมัติ (ไม่ค้างโชว์เป็น WIP อีกต่อไป) — กลับไปดูที่ MO ของ Stage 2 จะเห็นปุ่ม "Assembly MOs" เชื่อมมาที่ MO นี้แล้ว</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="n"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>งาน Custom ใช้ปุ่ม Produce ธรรมดาของ Odoo เลย (ตาม ADR-064 เดิม "มาตรฐาน ODOO") ต่างจาก Stage 2/G2 ที่มีปุ่มเฉพาะของโมดูล</t>
+        </is>
+      </c>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
       <c r="L8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M5-13</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>จัดส่ง ออกใบแจ้งหนี้ และรับชำระเงิน (Custom)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M5-12 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบส่งของที่เกิดขึ้นอัตโนมัติ &gt; Validate
+2. เปิด SO &gt; Create Invoice &gt; Regular Invoice &gt; Confirm
+3. เปิดใบแจ้งหนี้ &gt; Pay &gt; ยืนยันการชำระ</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>ใบส่งของ Done (ตัวอย่างจริง: EG01/OUT/00092) ใบแจ้งหนี้ Posted ยอด 12,840.00 (ตัวอย่างจริง: INV/2026/00038) แล้วขึ้น In Payment — Journal Items 5 บรรทัด สมดุล 12,916.89 = 12,916.89 (COGS 76.89 ไม่ใช่ 0)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
